--- a/data/trans_orig/P1422-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2012</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284366</t>
+          <t>284943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292869</t>
+          <t>293735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282144</t>
+          <t>282114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>570073</t>
+          <t>569657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580026</t>
+          <t>579999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483196</t>
+          <t>482534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500504</t>
+          <t>501242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511951</t>
+          <t>513013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522618</t>
+          <t>522641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1001409</t>
+          <t>1002426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021455</t>
+          <t>1021422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316233</t>
+          <t>316161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323113</t>
+          <t>323110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334457</t>
+          <t>332994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653914</t>
+          <t>654334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663140</t>
+          <t>663131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366297</t>
+          <t>365348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373067</t>
+          <t>373064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379056</t>
+          <t>379001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387902</t>
+          <t>387956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>749055</t>
+          <t>748562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760033</t>
+          <t>760004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203110</t>
+          <t>203788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211592</t>
+          <t>211596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210727</t>
+          <t>209647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218609</t>
+          <t>218592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417766</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429204</t>
+          <t>429194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269001</t>
+          <t>268009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270538</t>
+          <t>270535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542850</t>
+          <t>543626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551125</t>
+          <t>551115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655553</t>
+          <t>656209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>684174</t>
+          <t>683833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692812</t>
+          <t>692758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1344084</t>
+          <t>1343548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1354509</t>
+          <t>1354531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765438</t>
+          <t>766386</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776930</t>
+          <t>776854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>813606</t>
+          <t>813603</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821514</t>
+          <t>821517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1583448</t>
+          <t>1583862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597156</t>
+          <t>1596420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76057</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3376870</t>
+          <t>3378058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3403474</t>
+          <t>3403127</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3518042</t>
+          <t>3517256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3538481</t>
+          <t>3538501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6905820</t>
+          <t>6905823</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6937863</t>
+          <t>6937552</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2016</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286290</t>
+          <t>287547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292972</t>
+          <t>293761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288703</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575662</t>
+          <t>575601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581675</t>
+          <t>581672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489779</t>
+          <t>489119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500365</t>
+          <t>499733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>523084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012509</t>
+          <t>1013154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023502</t>
+          <t>1023434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311938</t>
+          <t>311951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317787</t>
+          <t>317791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331342</t>
+          <t>331273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646300</t>
+          <t>646307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654007</t>
+          <t>653885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362100</t>
+          <t>361320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372865</t>
+          <t>372886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385245</t>
+          <t>385224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>740537</t>
+          <t>740501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753445</t>
+          <t>753977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202518</t>
+          <t>202017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210274</t>
+          <t>210276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207916</t>
+          <t>207413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217385</t>
+          <t>217386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413337</t>
+          <t>414464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425667</t>
+          <t>425945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257835</t>
+          <t>259005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273115</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531481</t>
+          <t>531373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644712</t>
+          <t>647160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678836</t>
+          <t>679646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690120</t>
+          <t>690175</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332012</t>
+          <t>1332136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344723</t>
+          <t>1344749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>776592</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>814504</t>
+          <t>813614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825084</t>
+          <t>825083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1591891</t>
+          <t>1591778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362347</t>
+          <t>3362344</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3380746</t>
+          <t>3380405</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3509900</t>
+          <t>3512781</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3532154</t>
+          <t>3531773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6881902</t>
+          <t>6880284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6908087</t>
+          <t>6907771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2023</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307063</t>
+          <t>307294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286089</t>
+          <t>285944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595844</t>
+          <t>595615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600668</t>
+          <t>600650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505618</t>
+          <t>505555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514653</t>
+          <t>514354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506385</t>
+          <t>505608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513191</t>
+          <t>513046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1015380</t>
+          <t>1014898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026401</t>
+          <t>1026416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>301154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310951</t>
+          <t>310787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340969</t>
+          <t>341229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347329</t>
+          <t>347342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645162</t>
+          <t>645327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657101</t>
+          <t>656792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303955</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>467112</t>
+          <t>467546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473795</t>
+          <t>474045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>774326</t>
+          <t>774763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785037</t>
+          <t>785167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171333</t>
+          <t>171450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>177449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203193</t>
+          <t>203150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207073</t>
+          <t>207064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377082</t>
+          <t>376289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383543</t>
+          <t>383382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259353</t>
+          <t>258984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266405</t>
+          <t>266463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247964</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254159</t>
+          <t>254355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510402</t>
+          <t>510556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519640</t>
+          <t>519582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611539</t>
+          <t>611561</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>620874</t>
+          <t>620799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>834091</t>
+          <t>833354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>845318</t>
+          <t>844755</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1448948</t>
+          <t>1449551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1464101</t>
+          <t>1463948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911417</t>
+          <t>911095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925867</t>
+          <t>925118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703956</t>
+          <t>703331</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712209</t>
+          <t>712318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1618970</t>
+          <t>1618805</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635074</t>
+          <t>1635432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3401010</t>
+          <t>3401924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3425954</t>
+          <t>3425996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3611797</t>
+          <t>3612494</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3631145</t>
+          <t>3631711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7021918</t>
+          <t>7020125</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7053439</t>
+          <t>7053479</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P1422-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,82 +747,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5782</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11640</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5782</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>12326</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284943</t>
+          <t>284028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293735</t>
+          <t>292888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282114</t>
+          <t>282024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569657</t>
+          <t>570343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579999</t>
+          <t>579998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482534</t>
+          <t>483586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501242</t>
+          <t>501283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513013</t>
+          <t>512875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522641</t>
+          <t>522443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002426</t>
+          <t>1001933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021422</t>
+          <t>1021506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316161</t>
+          <t>316327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323110</t>
+          <t>323116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332994</t>
+          <t>333183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654334</t>
+          <t>653916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663131</t>
+          <t>663141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365348</t>
+          <t>366440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373064</t>
+          <t>373067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379001</t>
+          <t>378837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387956</t>
+          <t>387944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748562</t>
+          <t>749992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760004</t>
+          <t>760029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203788</t>
+          <t>204054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211596</t>
+          <t>211610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209647</t>
+          <t>209885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218592</t>
+          <t>218603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417920</t>
+          <t>417653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429194</t>
+          <t>429072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268009</t>
+          <t>268622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270535</t>
+          <t>271501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543626</t>
+          <t>543647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551115</t>
+          <t>551126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656209</t>
+          <t>656172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683833</t>
+          <t>683268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692758</t>
+          <t>692784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1343548</t>
+          <t>1343971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1354531</t>
+          <t>1354544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,42 +3188,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>9738</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>17515</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>9738</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>5256</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>17814</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766386</t>
+          <t>765675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776854</t>
+          <t>776919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>813603</t>
+          <t>813748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821517</t>
+          <t>821516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,47 +3296,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1591938</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1584161</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1597289</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,91%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1591938</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1583862</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1596420</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76054</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3378058</t>
+          <t>3378416</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3403127</t>
+          <t>3404420</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3517256</t>
+          <t>3517499</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3538501</t>
+          <t>3538568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6905823</t>
+          <t>6905936</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6937552</t>
+          <t>6937321</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4055,54 +4055,54 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6214</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287547</t>
+          <t>286270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293761</t>
+          <t>292973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,39 +4183,39 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>288703</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>288703</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575601</t>
+          <t>575286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581672</t>
+          <t>581675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489119</t>
+          <t>490158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499733</t>
+          <t>500388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013154</t>
+          <t>1012959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023434</t>
+          <t>1023430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311951</t>
+          <t>311993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317791</t>
+          <t>317788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331273</t>
+          <t>331254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646307</t>
+          <t>646256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653885</t>
+          <t>654005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361320</t>
+          <t>361734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369066</t>
+          <t>369061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372886</t>
+          <t>372765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385224</t>
+          <t>385242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>740501</t>
+          <t>741546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753977</t>
+          <t>754128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202017</t>
+          <t>202774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210276</t>
+          <t>210275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207413</t>
+          <t>207938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217386</t>
+          <t>217393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414464</t>
+          <t>412285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425945</t>
+          <t>425959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259005</t>
+          <t>257008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531373</t>
+          <t>531469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647160</t>
+          <t>645419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679646</t>
+          <t>679890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690175</t>
+          <t>690016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332136</t>
+          <t>1330992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344749</t>
+          <t>1344836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>813614</t>
+          <t>813084</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825083</t>
+          <t>825082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1591778</t>
+          <t>1591151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1603665</t>
+          <t>1602978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362344</t>
+          <t>3361575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3380405</t>
+          <t>3380353</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3512781</t>
+          <t>3511424</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3531773</t>
+          <t>3532233</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6880284</t>
+          <t>6880021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6907771</t>
+          <t>6909222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>976</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -7486,27 +7486,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310657</t>
+          <t>318157</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307294</t>
+          <t>316002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7521,27 +7521,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288631</t>
+          <t>315085</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285944</t>
+          <t>312397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7556,27 +7556,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>599287</t>
+          <t>633241</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595615</t>
+          <t>630451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600650</t>
+          <t>634483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511617</t>
+          <t>523619</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505555</t>
+          <t>517800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514354</t>
+          <t>526788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510620</t>
+          <t>542015</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505608</t>
+          <t>537049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513046</t>
+          <t>544543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1022238</t>
+          <t>1065634</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014898</t>
+          <t>1058061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026416</t>
+          <t>1069653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>515644</t>
+          <t>527811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>515644</t>
+          <t>527811</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>515644</t>
+          <t>527811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029935</t>
+          <t>1073620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029935</t>
+          <t>1073620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029935</t>
+          <t>1073620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,17 +8094,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>306967</t>
+          <t>306941</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301154</t>
+          <t>300402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310787</t>
+          <t>310894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,17 +8207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>344989</t>
+          <t>352153</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>341229</t>
+          <t>348091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347342</t>
+          <t>354605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>651956</t>
+          <t>659096</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645327</t>
+          <t>652492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656792</t>
+          <t>664046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8515,27 +8515,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>370269</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>361699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>471415</t>
+          <t>417444</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>467546</t>
+          <t>413119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474045</t>
+          <t>419788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>781371</t>
+          <t>787714</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>774763</t>
+          <t>780469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785167</t>
+          <t>791728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175251</t>
+          <t>202014</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171450</t>
+          <t>197942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177449</t>
+          <t>204367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>205580</t>
+          <t>223718</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203150</t>
+          <t>220913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207064</t>
+          <t>225352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>380831</t>
+          <t>425732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376289</t>
+          <t>421307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383382</t>
+          <t>428705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,17 +9088,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>263743</t>
+          <t>264773</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258984</t>
+          <t>260510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266463</t>
+          <t>267871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>252026</t>
+          <t>258537</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>254727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254355</t>
+          <t>260999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>515770</t>
+          <t>523309</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510556</t>
+          <t>517531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519582</t>
+          <t>527181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>617368</t>
+          <t>711096</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611561</t>
+          <t>704666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>620799</t>
+          <t>715439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>839996</t>
+          <t>759727</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>833354</t>
+          <t>752879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>844755</t>
+          <t>763853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1457365</t>
+          <t>1470823</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1449551</t>
+          <t>1462004</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1463948</t>
+          <t>1477384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848314</t>
+          <t>769996</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848314</t>
+          <t>769996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848314</t>
+          <t>769996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471875</t>
+          <t>1488815</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471875</t>
+          <t>1488815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471875</t>
+          <t>1488815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>919186</t>
+          <t>787350</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911095</t>
+          <t>779107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925118</t>
+          <t>791939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>709083</t>
+          <t>823400</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703331</t>
+          <t>817310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712318</t>
+          <t>826995</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1628269</t>
+          <t>1610750</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1618805</t>
+          <t>1601852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635432</t>
+          <t>1617151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54428</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3414746</t>
+          <t>3484220</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3401924</t>
+          <t>3471781</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3425996</t>
+          <t>3495090</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3622340</t>
+          <t>3692080</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3612494</t>
+          <t>3680286</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3631711</t>
+          <t>3700418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7037087</t>
+          <t>7176300</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7020125</t>
+          <t>7160989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7053479</t>
+          <t>7191374</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
